--- a/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 8,87</t>
+          <t>-17,08; 7,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,81; -1,53</t>
+          <t>-28,73; -1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 7,24</t>
+          <t>-16,27; 7,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 6,58</t>
+          <t>-22,07; 6,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 4,62</t>
+          <t>-13,82; 3,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 1,48</t>
+          <t>-20,88; 0,97</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 21,78</t>
+          <t>-31,88; 18,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,27; -4,48</t>
+          <t>-55,96; -3,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 14,24</t>
+          <t>-26,86; 14,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 13,06</t>
+          <t>-36,24; 12,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 9,43</t>
+          <t>-24,17; 7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 2,4</t>
+          <t>-37,95; 1,96</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,52; -6,65</t>
+          <t>-23,32; -6,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,1; -2,62</t>
+          <t>-23,81; -1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,46; -2,06</t>
+          <t>-20,33; -1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 3,81</t>
+          <t>-19,42; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,26; -7,18</t>
+          <t>-19,15; -6,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -0,6</t>
+          <t>-18,28; -0,41</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,64; -17,02</t>
+          <t>-50,47; -17,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,74; -6,97</t>
+          <t>-51,53; -3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -4,14</t>
+          <t>-33,36; -2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 7,57</t>
+          <t>-31,9; 6,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,66; -15,38</t>
+          <t>-36,13; -14,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,6; -1,41</t>
+          <t>-34,5; -0,85</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,09; -0,44</t>
+          <t>-19,6; -0,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-38,87; -2,22</t>
+          <t>-40,69; -2,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,48; -3,76</t>
+          <t>-24,2; -4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,05; -3,47</t>
+          <t>-28,7; -3,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,3; -4,96</t>
+          <t>-18,88; -4,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,47; -8,02</t>
+          <t>-31,93; -7,85</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,31; -1,1</t>
+          <t>-40,97; -1,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,6; -4,16</t>
+          <t>-82,78; -6,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,16; -7,87</t>
+          <t>-43,99; -8,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,01; -7,81</t>
+          <t>-53,86; -8,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,28; -11,43</t>
+          <t>-38,11; -12,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,96; -17,88</t>
+          <t>-65,5; -17,68</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 1,5</t>
+          <t>-19,12; 1,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-29,7; -5,96</t>
+          <t>-30,47; -6,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,56</t>
+          <t>-11,35; 6,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -6,58</t>
+          <t>-30,51; -6,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 2,12</t>
+          <t>-12,41; 2,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -10,26</t>
+          <t>-26,93; -9,91</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 3,46</t>
+          <t>-36,18; 4,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,21; -13,51</t>
+          <t>-58,49; -12,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 14,81</t>
+          <t>-20,29; 14,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,14; -14,16</t>
+          <t>-57,44; -12,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 4,52</t>
+          <t>-23,34; 4,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,7; -21,67</t>
+          <t>-52,79; -20,98</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -5,42</t>
+          <t>-15,21; -5,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -10,3</t>
+          <t>-25,83; -9,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -3,08</t>
+          <t>-13,17; -3,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -6,51</t>
+          <t>-18,72; -5,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -5,54</t>
+          <t>-12,62; -5,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,54; -9,67</t>
+          <t>-19,41; -9,09</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -12,81</t>
+          <t>-32,32; -12,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -23,86</t>
+          <t>-56,28; -22,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,46; -6,07</t>
+          <t>-23,62; -6,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,79; -12,35</t>
+          <t>-33,57; -11,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,12; -11,73</t>
+          <t>-24,67; -10,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,25; -20,06</t>
+          <t>-39,11; -18,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 7,41</t>
+          <t>-17,51; 7,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,73; -1,53</t>
+          <t>-28,39; -0,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 7,61</t>
+          <t>-17,16; 7,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 6,18</t>
+          <t>-22,04; 7,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 3,35</t>
+          <t>-12,98; 4,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 0,97</t>
+          <t>-20,12; 0,6</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 18,28</t>
+          <t>-33,38; 17,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,96; -3,11</t>
+          <t>-54,05; 1,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 14,19</t>
+          <t>-27,75; 14,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 12,85</t>
+          <t>-36,35; 14,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 7,58</t>
+          <t>-23,49; 8,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 1,96</t>
+          <t>-37,11; 0,8</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,32; -6,81</t>
+          <t>-23,51; -5,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,81; -1,65</t>
+          <t>-23,24; -1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -1,2</t>
+          <t>-21,4; -2,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 3,3</t>
+          <t>-20,66; 2,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,15; -6,87</t>
+          <t>-20,04; -7,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -0,41</t>
+          <t>-17,4; -0,48</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,47; -17,41</t>
+          <t>-50,09; -15,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,53; -3,78</t>
+          <t>-50,94; -2,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,36; -2,6</t>
+          <t>-34,35; -5,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 6,26</t>
+          <t>-33,58; 4,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,13; -14,79</t>
+          <t>-37,65; -15,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,5; -0,85</t>
+          <t>-33,08; -0,94</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -0,28</t>
+          <t>-19,04; 0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-40,69; -2,75</t>
+          <t>-40,62; -3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,2; -4,17</t>
+          <t>-24,43; -3,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,7; -3,16</t>
+          <t>-28,2; -2,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,88; -4,93</t>
+          <t>-19,95; -4,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,93; -7,85</t>
+          <t>-33,46; -8,36</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,97; -1,36</t>
+          <t>-38,94; 3,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,78; -6,38</t>
+          <t>-81,5; -6,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -8,66</t>
+          <t>-44,98; -7,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,86; -8,05</t>
+          <t>-52,89; -5,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,11; -12,62</t>
+          <t>-39,29; -10,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,5; -17,68</t>
+          <t>-65,69; -18,98</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 1,97</t>
+          <t>-18,19; 2,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-30,47; -6,0</t>
+          <t>-29,06; -4,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 6,76</t>
+          <t>-11,25; 7,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,51; -6,16</t>
+          <t>-30,95; -7,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 2,0</t>
+          <t>-11,35; 2,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,93; -9,91</t>
+          <t>-26,88; -9,87</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 4,98</t>
+          <t>-34,4; 4,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,49; -12,59</t>
+          <t>-57,22; -10,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 14,72</t>
+          <t>-20,46; 15,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,44; -12,81</t>
+          <t>-57,24; -14,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 4,45</t>
+          <t>-22,11; 4,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,79; -20,98</t>
+          <t>-52,07; -20,7</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -5,1</t>
+          <t>-15,64; -5,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -9,64</t>
+          <t>-25,94; -10,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -3,12</t>
+          <t>-12,95; -2,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -5,93</t>
+          <t>-19,57; -5,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -5,21</t>
+          <t>-12,47; -5,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -9,09</t>
+          <t>-20,57; -9,61</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -12,23</t>
+          <t>-32,68; -12,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,28; -22,13</t>
+          <t>-56,06; -23,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,62; -6,22</t>
+          <t>-23,08; -4,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,57; -11,34</t>
+          <t>-35,04; -10,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -10,96</t>
+          <t>-24,67; -11,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,11; -18,97</t>
+          <t>-40,7; -19,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-7,67</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-5,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-15,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,9</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,23</t>
+          <t>-16,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,79</t>
+          <t>-10,77</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 7,58</t>
+          <t>-15,81; 7,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,39; -0,12</t>
+          <t>-23,14; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 7,0</t>
+          <t>-16,11; 8,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 7,34</t>
+          <t>-28,75; -2,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 4,28</t>
+          <t>-13,46; 4,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 0,6</t>
+          <t>-21,03; 0,45</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-8,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-13,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-10,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-32,22%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-8,68%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-12,82%</t>
+          <t>-34,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,9%</t>
+          <t>-20,79%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 17,65</t>
+          <t>-26,04; 14,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 1,06</t>
+          <t>-37,81; 12,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 14,36</t>
+          <t>-30,75; 21,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 14,9</t>
+          <t>-56,01; -6,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 8,97</t>
+          <t>-24,15; 9,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 0,8</t>
+          <t>-38,12; 1,24</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-11,7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-9,15</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-14,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-13,43</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-11,7</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-9,26</t>
+          <t>-13,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,29</t>
+          <t>-9,63</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,51; -5,95</t>
+          <t>-20,46; -2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,24; -1,65</t>
+          <t>-19,47; 4,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,4; -2,82</t>
+          <t>-23,52; -6,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 2,96</t>
+          <t>-24,56; -2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,04; -7,19</t>
+          <t>-20,26; -7,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,4; -0,48</t>
+          <t>-18,27; -1,57</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-20,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-15,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-35,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-31,93%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-20,22%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-16,0%</t>
+          <t>-32,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-18,47%</t>
+          <t>-19,14%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -15,2</t>
+          <t>-32,68; -4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,94; -2,5</t>
+          <t>-32,52; 8,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,35; -5,21</t>
+          <t>-50,64; -17,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 4,93</t>
+          <t>-54,85; -6,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,65; -15,34</t>
+          <t>-37,66; -15,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,08; -0,94</t>
+          <t>-34,25; -3,25</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-14,12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-16,7</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-10,42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-20,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-14,12</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-16,22</t>
+          <t>-16,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-18,55</t>
+          <t>-16,38</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 0,99</t>
+          <t>-24,48; -3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-40,62; -3,21</t>
+          <t>-27,98; -3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -3,38</t>
+          <t>-20,09; -0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,2; -2,31</t>
+          <t>-28,3; -2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,95; -4,63</t>
+          <t>-19,3; -4,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,46; -8,36</t>
+          <t>-25,26; -7,04</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-28,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-33,71%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-23,48%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-46,37%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-28,51%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-32,75%</t>
+          <t>-37,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-39,51%</t>
+          <t>-34,88%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 3,17</t>
+          <t>-45,16; -7,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,5; -6,86</t>
+          <t>-53,79; -8,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,98; -7,23</t>
+          <t>-41,31; -1,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,89; -5,12</t>
+          <t>-59,61; -6,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,29; -10,64</t>
+          <t>-38,28; -11,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -18,98</t>
+          <t>-51,33; -15,69</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-18,9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-8,2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-18,1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-19,27</t>
+          <t>-21,08</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-18,72</t>
+          <t>-20,1</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 2,07</t>
+          <t>-12,25; 6,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-29,06; -4,69</t>
+          <t>-30,94; -6,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 7,09</t>
+          <t>-18,28; 1,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,95; -7,08</t>
+          <t>-32,39; -9,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 2,23</t>
+          <t>-12,18; 2,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,88; -9,87</t>
+          <t>-28,28; -11,86</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-37,33%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-17,32%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-38,23%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,42%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-38,07%</t>
+          <t>-44,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-38,21%</t>
+          <t>-41,03%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 4,85</t>
+          <t>-22,69; 14,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,22; -10,37</t>
+          <t>-57,39; -12,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 15,76</t>
+          <t>-36,16; 3,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,24; -14,89</t>
+          <t>-63,34; -23,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 4,87</t>
+          <t>-23,54; 4,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,07; -20,7</t>
+          <t>-54,76; -25,0</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-8,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-12,6</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-10,25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-17,3</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-8,33</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-12,64</t>
+          <t>-17,07</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-14,48</t>
+          <t>-14,2</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -5,22</t>
+          <t>-13,25; -3,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,94; -10,11</t>
+          <t>-18,77; -6,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -2,37</t>
+          <t>-15,41; -5,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -5,75</t>
+          <t>-22,85; -10,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -5,26</t>
+          <t>-12,74; -5,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -9,61</t>
+          <t>-18,7; -9,74</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-15,51%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-23,47%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-22,77%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-38,41%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-15,51%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-23,54%</t>
+          <t>-37,89%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-29,27%</t>
+          <t>-28,71%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -12,41</t>
+          <t>-23,46; -6,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -23,2</t>
+          <t>-33,86; -12,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -4,45</t>
+          <t>-32,92; -12,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -10,95</t>
+          <t>-49,05; -24,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -11,26</t>
+          <t>-25,12; -11,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-40,7; -19,83</t>
+          <t>-36,97; -20,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Habitat-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-4.897332732744742</v>
+        <v>-4.007024540713133</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-7.668621989437069</v>
+        <v>-3.700309559975112</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-5.042243997074635</v>
+        <v>-7.688367294511384</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-16.01988754289959</v>
+        <v>-14.25566725647052</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-4.855965741674617</v>
+        <v>-5.604910252520795</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-10.76816175446347</v>
+        <v>-7.721979898273856</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-15.80906135367514</v>
+        <v>-15.63258108473711</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-23.13594547314389</v>
+        <v>-18.08055982251593</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-16.11113442161429</v>
+        <v>-18.31373957997133</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-28.7529031033882</v>
+        <v>-27.54745748085432</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-13.45553990282623</v>
+        <v>-13.56778494155583</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-21.03241155468382</v>
+        <v>-18.00321472577209</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7.241790135237296</v>
+        <v>6.394209648217887</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6.196729778067509</v>
+        <v>10.65688673465094</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>8.874577979542895</v>
+        <v>4.346220364132281</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-2.753182506710868</v>
+        <v>1.281935009271455</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.618088824570011</v>
+        <v>2.125519161246022</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.4506635588423356</v>
+        <v>2.315641672215584</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.08679590037132179</v>
+        <v>-0.0738323676719851</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.1359117271591765</v>
+        <v>-0.06818091907258991</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.1077167334868614</v>
+        <v>-0.1663011418335505</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.3422305540844822</v>
+        <v>-0.3083533410328405</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.09374707946927353</v>
+        <v>-0.1112949161913193</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2078852630837447</v>
+        <v>-0.1533328932827998</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.2604056431750259</v>
+        <v>-0.2653086750035955</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.3781405653128557</v>
+        <v>-0.320074806444288</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.3074821919777815</v>
+        <v>-0.3597800110698597</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.5600818601035389</v>
+        <v>-0.5355619387863967</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.2415094049195474</v>
+        <v>-0.2578366763379004</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.3811949370736973</v>
+        <v>-0.3425296916409103</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.1423659751106799</v>
+        <v>0.1211341917499498</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.1268072637962424</v>
+        <v>0.2124978027260404</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.2178286769239159</v>
+        <v>0.1066510139520193</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.06884679165299387</v>
+        <v>0.03713451907083719</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.09433959059217317</v>
+        <v>0.04228645780157203</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.0124195251105755</v>
+        <v>0.04239879442450877</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-11.6979510384525</v>
+        <v>-9.295448714220772</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-9.153002317863463</v>
+        <v>-7.023658598416493</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-14.94604691578017</v>
+        <v>-15.59436871441285</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-13.75403529339317</v>
+        <v>-13.35779362907165</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-13.44719132056489</v>
+        <v>-12.33237136249591</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-9.628950179682928</v>
+        <v>-8.397446416828396</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-20.45666701214111</v>
+        <v>-17.4611383054521</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-19.46980295534355</v>
+        <v>-17.54324367538423</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-23.51702756464372</v>
+        <v>-22.87649819156982</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-24.56165452906341</v>
+        <v>-24.16818065068735</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-20.26377643045489</v>
+        <v>-18.30216240542117</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-18.26951162927197</v>
+        <v>-16.08814361647224</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-2.057398927868917</v>
+        <v>-0.3265913606436394</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4.550051766820156</v>
+        <v>3.53543508098745</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-6.646530778403313</v>
+        <v>-6.299314466021241</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-2.652463782672086</v>
+        <v>-2.808599540444325</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-7.1802518805495</v>
+        <v>-6.210576081617993</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-1.565358668230492</v>
+        <v>-0.4741649780049461</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.2021771341032617</v>
+        <v>-0.1709159792686177</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.1581924707141661</v>
+        <v>-0.129144436627386</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.3552938744766203</v>
+        <v>-0.3706295568732865</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.3269576575407636</v>
+        <v>-0.3174731356051587</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2672812710556113</v>
+        <v>-0.2546345003572115</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.1913885198480761</v>
+        <v>-0.1733875432204626</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.326804312336708</v>
+        <v>-0.3010359363041281</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.3251612693651439</v>
+        <v>-0.2999615298286679</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.5064148538332883</v>
+        <v>-0.5060641453870112</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.5485250405532421</v>
+        <v>-0.5275779622633654</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.376619437001452</v>
+        <v>-0.3624400557841857</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.3425112536095479</v>
+        <v>-0.3197088907167245</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.04137995404311569</v>
+        <v>-0.005733690217568415</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.08955372053461537</v>
+        <v>0.07011172189833517</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.1702150411780907</v>
+        <v>-0.1683604955466382</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.0644064139624532</v>
+        <v>-0.07538961269290072</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1537808930907387</v>
+        <v>-0.1424861145327717</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.03245121291770915</v>
+        <v>-0.01092192190213192</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-14.12186491173851</v>
+        <v>-11.34273895250104</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-16.69672038701724</v>
+        <v>-17.09034001139867</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-10.41793815231773</v>
+        <v>-9.14900488741805</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-16.64179555359757</v>
+        <v>-16.26098245724568</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-12.2526202549871</v>
+        <v>-10.25109211028172</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-16.37595544221289</v>
+        <v>-16.56417502805361</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-24.47946336400786</v>
+        <v>-21.21806011174465</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-27.97535809337383</v>
+        <v>-29.86543306080938</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-20.08782209385454</v>
+        <v>-18.31196281459835</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-28.30455534105133</v>
+        <v>-26.94208433408409</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-19.29894044106732</v>
+        <v>-17.11440561734268</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-25.25583683013252</v>
+        <v>-25.00594864671309</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-3.763682517497339</v>
+        <v>-1.901435829860962</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-3.349992091581114</v>
+        <v>-5.497449797756078</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.4390905551403095</v>
+        <v>-0.1344373128636824</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-2.858815818980234</v>
+        <v>-2.205172447385482</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-4.958035649678258</v>
+        <v>-3.246566858532232</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-7.04464893549051</v>
+        <v>-6.936456041772578</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.2851237469224284</v>
+        <v>-0.2292743392053628</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.3371106796316453</v>
+        <v>-0.3454524016921338</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.2348328087772605</v>
+        <v>-0.2022469825134418</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.3751260120582307</v>
+        <v>-0.359463643877238</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.2609512574661263</v>
+        <v>-0.2162189222143149</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.3487683512524895</v>
+        <v>-0.3493762453214942</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.4515546358123555</v>
+        <v>-0.3971815583608487</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.5378620115960635</v>
+        <v>-0.550206446680047</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.4130562246449102</v>
+        <v>-0.370513389336156</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.596058007958371</v>
+        <v>-0.5519361676024527</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.3827753723904289</v>
+        <v>-0.3319024526310163</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.5132547399526306</v>
+        <v>-0.4965948405703768</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>-0.07872650939742479</v>
+        <v>-0.04614125408697796</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-0.08564463475439255</v>
+        <v>-0.1136196444119596</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-0.01100434292503773</v>
+        <v>-0.009087873583224241</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.06590557259035837</v>
+        <v>-0.05549270569105411</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.1143405485587921</v>
+        <v>-0.07234847004630608</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.1569032352793276</v>
+        <v>-0.1532072784306548</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-2.238342287485429</v>
+        <v>-2.564928001861155</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-18.89711846324925</v>
+        <v>-17.02336643732819</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-8.20012408816776</v>
+        <v>-8.896328043493561</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-21.07743897658184</v>
+        <v>-19.60039587175704</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-5.054561492676902</v>
+        <v>-5.552430280938148</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-20.09990114470705</v>
+        <v>-18.41631940706123</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-12.25357366289712</v>
+        <v>-11.68791497270315</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-30.94446160492739</v>
+        <v>-28.08916880443231</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-18.28367016110808</v>
+        <v>-18.71638474035928</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-32.38976888875823</v>
+        <v>-30.0932839499362</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-12.1763551912667</v>
+        <v>-11.9302576306616</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-28.28082340066091</v>
+        <v>-26.23291323016478</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>6.564959952413618</v>
+        <v>5.913592059437658</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-6.104347566544064</v>
+        <v>-5.372894426880892</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1.496639644784788</v>
+        <v>0.8914019425402278</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-9.95917255557049</v>
+        <v>-9.079979942446757</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.119478400798135</v>
+        <v>0.6372174998583787</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-11.86377353705326</v>
+        <v>-10.24525440370842</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.04422020338554066</v>
+        <v>-0.05184178176141137</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.3733273621811862</v>
+        <v>-0.344072678472117</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.1731864652450105</v>
+        <v>-0.1918567909663694</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.4451551114987154</v>
+        <v>-0.4226990096634357</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1031757644485894</v>
+        <v>-0.115819269833771</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.4102873550852635</v>
+        <v>-0.3841497432347676</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.2268898262720672</v>
+        <v>-0.2145028310751643</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.5738549017643465</v>
+        <v>-0.5425380954873437</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.361615523541076</v>
+        <v>-0.3708920516279194</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.6333613731630735</v>
+        <v>-0.6020033181835728</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.2354427571077657</v>
+        <v>-0.2368034697190161</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.5475538027725804</v>
+        <v>-0.5254125047720893</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.1481151640846134</v>
+        <v>0.1281766934733405</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>-0.1285604976868965</v>
+        <v>-0.1219701364812303</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.03457345136633513</v>
+        <v>0.02670309299740671</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2394495029708287</v>
+        <v>-0.1999531564012555</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.04520155351322457</v>
+        <v>0.01365961583807967</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.2500158780052732</v>
+        <v>-0.2250381283976571</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-8.32579242345629</v>
+        <v>-6.958859408935991</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-12.60069356068003</v>
+        <v>-10.87125575883014</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-10.25460147098062</v>
+        <v>-10.70933135887874</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-17.06825775079078</v>
+        <v>-16.06145267180248</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-9.191923394149647</v>
+        <v>-8.677639236170853</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-14.2007569465679</v>
+        <v>-12.87706306270158</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-13.25042111320459</v>
+        <v>-11.63589059199919</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-18.76659200769538</v>
+        <v>-17.00494092666229</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-15.40815857156266</v>
+        <v>-15.40827692272912</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-22.84995588658888</v>
+        <v>-21.49067144938049</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-12.73581157673944</v>
+        <v>-11.96284746678382</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-18.69903729521868</v>
+        <v>-17.17436358614127</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-3.081794520635174</v>
+        <v>-2.131597794921965</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-6.635647397371643</v>
+        <v>-4.210654515134935</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-5.419832303612407</v>
+        <v>-5.954766706598869</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-10.41090064567243</v>
+        <v>-9.142804562176991</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-5.541073835820444</v>
+        <v>-5.416984652203325</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-9.744870110091576</v>
+        <v>-8.602605151423765</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.1550759644441405</v>
+        <v>-0.1339769113739462</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.2347001471094009</v>
+        <v>-0.209301148900059</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.2276652148271062</v>
+        <v>-0.2389945580816009</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.3789370633812267</v>
+        <v>-0.3584350558229324</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.1858428352979701</v>
+        <v>-0.1790609693768958</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.2871117198395308</v>
+        <v>-0.2657150559017968</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.2346496920150425</v>
+        <v>-0.2149353384214662</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.3386070483581766</v>
+        <v>-0.3184251897886948</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.329164891411815</v>
+        <v>-0.3268659071585072</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.4905184027618657</v>
+        <v>-0.4700625846438216</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.2511580052419535</v>
+        <v>-0.2385459607558895</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.3696889872857413</v>
+        <v>-0.3476580540860886</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0.06074887369775376</v>
+        <v>-0.04763772599944401</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>-0.1281302121978793</v>
+        <v>-0.08789696238405113</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-0.1280573769471604</v>
+        <v>-0.1412282835570448</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.2441911100374952</v>
+        <v>-0.212911852004096</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.1172772872610775</v>
+        <v>-0.1139575865841379</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.2013796972570646</v>
+        <v>-0.1850933172479575</v>
       </c>
     </row>
     <row r="34">
